--- a/frontend/kskcolle/public/data/erelijsten/Records.xlsx
+++ b/frontend/kskcolle/public/data/erelijsten/Records.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/Website KSK Colle/_/erelijsten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/KSKColle/frontend/kskcolle/public/data/erelijsten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{32A12511-A139-463B-98BD-307D6A871AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{592065DF-C89A-4215-A394-1A5FC3B1C6B1}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{32A12511-A139-463B-98BD-307D6A871AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D92728-87E7-4B4D-9C66-1B265FA1DD0A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Records" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="25">
   <si>
     <t>Winnaars Clubkampioenschap en Snelschaakkampioenschap in hetzelfde jaar</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>2022</t>
+  </si>
+  <si>
+    <t>Pieter-Jan Orban</t>
   </si>
 </sst>
 </file>
@@ -234,6 +237,15 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -241,15 +253,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -599,14 +602,14 @@
   <sheetData>
     <row r="1" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -761,14 +764,14 @@
     </row>
     <row r="12" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="8"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -893,14 +896,14 @@
     </row>
     <row r="21" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -954,14 +957,14 @@
     </row>
     <row r="27" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
@@ -1040,14 +1043,14 @@
     </row>
     <row r="34" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="8"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="11"/>
     </row>
     <row r="36" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
@@ -1103,17 +1106,23 @@
       <c r="E39" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="F39" s="2">
+        <v>2026</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="40" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="8"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="11"/>
     </row>
     <row r="42" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
@@ -1317,14 +1326,14 @@
     </row>
     <row r="65" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="11"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="8"/>
     </row>
     <row r="67" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
@@ -1338,17 +1347,17 @@
     <row r="69" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B35:G35"/>
     <mergeCell ref="B66:G66"/>
     <mergeCell ref="B41:G41"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="B62:G62"/>
     <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B35:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
